--- a/Sample Data/SOLD_REPORT.xlsx
+++ b/Sample Data/SOLD_REPORT.xlsx
@@ -1,139 +1,165 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="5"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="135" windowWidth="27795" windowHeight="12600"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
-    <sheet name="ورقة2" sheetId="2" r:id="rId2"/>
-    <sheet name="ورقة3" sheetId="3" r:id="rId3"/>
+    <sheet name="ورقة1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="ورقة2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="ورقة3" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="32">
-  <si>
-    <t>المبيعات</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="33">
+  <si>
+    <t xml:space="preserve">المبيعات</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>مردود المبيعات</t>
-  </si>
-  <si>
-    <t>صافي المبيعات</t>
-  </si>
-  <si>
-    <t>رقم الصنف</t>
-  </si>
-  <si>
-    <t>اسم الصنف</t>
-  </si>
-  <si>
-    <t>الوحدة</t>
-  </si>
-  <si>
-    <t>العملة</t>
-  </si>
-  <si>
-    <t>الكمية</t>
-  </si>
-  <si>
-    <t>ك.المجانيه</t>
-  </si>
-  <si>
-    <t>المبلغ</t>
-  </si>
-  <si>
-    <t>مبلغ الصافي بالمحلي</t>
-  </si>
-  <si>
-    <t>3E7577</t>
-  </si>
-  <si>
-    <t>ALTERNATOR GP</t>
-  </si>
-  <si>
-    <t>حبة</t>
-  </si>
-  <si>
-    <t>SAR</t>
-  </si>
-  <si>
-    <t>1R0749J</t>
-  </si>
-  <si>
-    <t>FULE FILTER FF5264 فلتر ديزل</t>
-  </si>
-  <si>
-    <t>20Y-04-11160H</t>
-  </si>
-  <si>
-    <t>CAP 2A7-04-11260//HEP-CHINA</t>
-  </si>
-  <si>
-    <t>1W7550H</t>
-  </si>
-  <si>
-    <t>GAUGE ساعة حرارة المكينة</t>
-  </si>
-  <si>
-    <t>1M9011</t>
-  </si>
-  <si>
-    <t>سيلة الشيال  980C</t>
-  </si>
-  <si>
-    <t>2W8003JR</t>
-  </si>
-  <si>
-    <t>طرمباء ماء WATER PUMP</t>
-  </si>
-  <si>
-    <t>07020-00000E</t>
-  </si>
-  <si>
-    <t>GREASE FITTING//HM-K33001/CHINA</t>
-  </si>
-  <si>
-    <t>2W8002H</t>
-  </si>
-  <si>
-    <t>طرمبة ماء WATER PUMP</t>
-  </si>
-  <si>
-    <t>07000-15410</t>
-  </si>
-  <si>
-    <t>O-RING</t>
+    <t xml:space="preserve">مردود المبيعات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صافي المبيعات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رقم الصنف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسم الصنف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الوحدة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العملة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الكمية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ك.المجانيه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المبلغ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مبلغ الصافي بالمحلي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3E7577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTERNATOR GP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حبة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1R0749J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FULE FILTER FF5264 فلتر ديزل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20Y-04-11160H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAP 2A7-04-11260//HEP-CHINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1W7550H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAUGE ساعة حرارة المكينة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1M9011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سيلة الشيال  980C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2W8003JR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">طرمباء ماء WATER PUMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07020-00000E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GREASE FITTING//HM-K33001/CHINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2W8002H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">طرمبة ماء WATER PUMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07000-15410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O-RING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLK-320</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="178"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="13"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -145,31 +171,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="20"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF800080"/>
+        <bgColor rgb="FF800080"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="25"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF993366"/>
+        <bgColor rgb="FF993366"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="24"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF9999FF"/>
+        <bgColor rgb="FFCC99FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="22"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFC0C0C0"/>
+        <bgColor rgb="FFCCCCFF"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -177,39 +203,77 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="نسق Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="نسق Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -244,7 +308,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -279,7 +343,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -314,200 +378,153 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:N12"/>
+  <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.875" bestFit="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="5.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="5.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="8.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="8.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="11.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.88"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
@@ -536,7 +553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -580,422 +597,453 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>1648.9985227658799</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="F3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>1648.99852276588</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>1648.9985227658799</v>
-      </c>
-      <c r="N3">
-        <v>1648.9985227658799</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="0" t="n">
+        <v>1648.99852276588</v>
+      </c>
+      <c r="N3" s="0" t="n">
+        <v>1648.99852276588</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="0" t="n">
         <v>942</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>37408.316839040097</v>
-      </c>
-      <c r="H4">
+      <c r="F4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>37408.3168390401</v>
+      </c>
+      <c r="H4" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>961.44325064237705</v>
-      </c>
-      <c r="K4">
+      <c r="I4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>961.443250642377</v>
+      </c>
+      <c r="K4" s="0" t="n">
         <v>918</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>36446.873588397699</v>
-      </c>
-      <c r="N4">
-        <v>36446.873588397699</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="0" t="n">
+        <v>36446.8735883977</v>
+      </c>
+      <c r="N4" s="0" t="n">
+        <v>36446.8735883977</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
+      <c r="F5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="0" t="n">
         <v>86.96</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
+      <c r="H5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="0" t="n">
         <v>86.96</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="0" t="n">
         <v>86.96</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="0" t="n">
         <v>283</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
+      <c r="F6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="0" t="n">
         <v>17036.6400107068</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>871.30240000000003</v>
-      </c>
-      <c r="K6">
+      <c r="I6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>871.3024</v>
+      </c>
+      <c r="K6" s="0" t="n">
         <v>269</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
+      <c r="L6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="0" t="n">
         <v>16165.3376107068</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="0" t="n">
         <v>16165.3376107068</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>516.66251378670097</v>
-      </c>
-      <c r="H7">
+      <c r="F7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>516.662513786701</v>
+      </c>
+      <c r="H7" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
+      <c r="I7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="0" t="n">
         <v>34.78</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="0" t="n">
         <v>22</v>
       </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
+      <c r="L7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="0" t="n">
         <v>481.882513786701</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="0" t="n">
         <v>481.882513786701</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="0" t="n">
         <v>29</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>20785.716687715201</v>
-      </c>
-      <c r="H8">
+      <c r="F8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>20785.7166877152</v>
+      </c>
+      <c r="H8" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>2217.3910000000001</v>
-      </c>
-      <c r="K8">
+      <c r="I8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>2217.391</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <v>26</v>
       </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>18568.325687715202</v>
-      </c>
-      <c r="N8">
-        <v>18568.325687715202</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="0" t="n">
+        <v>18568.3256877152</v>
+      </c>
+      <c r="N8" s="0" t="n">
+        <v>18568.3256877152</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="0" t="n">
         <v>1132</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>2318.3667600754802</v>
-      </c>
-      <c r="H9">
+      <c r="F9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>2318.36676007548</v>
+      </c>
+      <c r="H9" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
+      <c r="I9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="0" t="n">
         <v>39.14</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="0" t="n">
         <v>1114</v>
       </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>2279.2267600754799</v>
-      </c>
-      <c r="N9">
-        <v>2279.2267600754799</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="0" t="n">
+        <v>2279.22676007548</v>
+      </c>
+      <c r="N9" s="0" t="n">
+        <v>2279.22676007548</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="0" t="n">
         <v>27</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>12457.717756210501</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
+      <c r="F10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>12457.7177562105</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="0" t="n">
         <v>27</v>
       </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>12457.717756210501</v>
-      </c>
-      <c r="N10">
-        <v>12457.717756210501</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="0" t="n">
+        <v>12457.7177562105</v>
+      </c>
+      <c r="N10" s="0" t="n">
+        <v>12457.7177562105</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="0" t="n">
         <v>49</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
+      <c r="F11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="0" t="n">
         <v>1694.48786586337</v>
       </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
+      <c r="H11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="0" t="n">
         <v>49</v>
       </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
+      <c r="L11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="0" t="n">
         <v>1694.48786586337</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="0" t="n">
         <v>1694.48786586337</v>
       </c>
     </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>